--- a/314e-ig/output/StructureDefinition-encounter-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-encounter-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -309,7 +309,7 @@
     <t>Encounter.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta
+    <t xml:space="preserve">Meta {http://314e.com/fhir/StructureDefinition/meta-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-encounter-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-encounter-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-encounter-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-encounter-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-encounter-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-encounter-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-encounter-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-encounter-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1067,7 +1067,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1095,7 +1095,7 @@
     <t>Encounter.episodeOfCare</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(EpisodeOfCare) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/episodeofcare-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1121,7 +1121,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/servicerequest-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1206,7 +1206,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-practitioner|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-practitionerrole|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-relatedperson) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1234,7 +1234,7 @@
     <t>Encounter.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Appointment) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/appointment-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1337,7 +1337,7 @@
     <t>Encounter.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-condition-problems-health-concerns|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-condition-encounter-diagnosis|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-procedure|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-simple-observation|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-immunizationrecommendation) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/procedure-314e|http://314e.com/fhir/StructureDefinition/immunizationrecommendation-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1372,7 +1372,7 @@
 discharge diagnosisindication</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Procedure) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/procedure-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1425,7 +1425,7 @@
     <t>Encounter.account</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Account) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/account-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1486,7 +1486,7 @@
     <t>Encounter.hospitalization.origin</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-location) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/location-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1734,7 +1734,7 @@
     <t>Encounter.serviceProvider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1753,7 +1753,7 @@
     <t>Encounter.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-encounter-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-encounter-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-encounter-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-encounter-314e.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$92</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3286" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3322" uniqueCount="570">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -634,6 +634,22 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>Encounter.extension:modeOfArrival</t>
+  </si>
+  <si>
+    <t>modeOfArrival</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/encounter-modeOfArrival-314e}
+</t>
+  </si>
+  <si>
+    <t>How the patient arrived at the reporting facility</t>
+  </si>
+  <si>
+    <t>Identifies how the patient arrives at the reporting facility, for example via an ambulance or other mode of transport.</t>
   </si>
   <si>
     <t>Encounter.modifierExtension</t>
@@ -2088,12 +2104,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN91"/>
+  <dimension ref="A1:AN92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.34765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.34765625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -4187,43 +4203,41 @@
         <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="D19" t="s" s="2">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>20</v>
       </c>
@@ -4271,7 +4285,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4280,7 +4294,7 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>116</v>
@@ -4289,7 +4303,7 @@
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>20</v>
@@ -4298,7 +4312,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>202</v>
       </c>
@@ -4307,7 +4321,7 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4317,25 +4331,29 @@
         <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I20" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I20" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="J20" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>20</v>
       </c>
@@ -4383,7 +4401,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4395,27 +4413,27 @@
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AM20" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="21" hidden="true">
-      <c r="A21" t="s" s="2">
-        <v>210</v>
-      </c>
       <c r="B21" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4426,25 +4444,25 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>101</v>
+        <v>208</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>102</v>
+        <v>209</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>103</v>
+        <v>210</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4495,50 +4513,50 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>104</v>
+        <v>207</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>20</v>
+        <v>211</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>105</v>
+        <v>212</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>20</v>
+        <v>213</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>20</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4550,17 +4568,15 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4597,31 +4613,31 @@
         <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
@@ -4638,46 +4654,44 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>213</v>
+        <v>109</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>20</v>
       </c>
@@ -4701,63 +4715,63 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>218</v>
+        <v>20</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>219</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>115</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>221</v>
+        <v>105</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4774,25 +4788,25 @@
         <v>20</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>223</v>
+        <v>163</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4817,13 +4831,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>145</v>
+        <v>222</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4841,7 +4855,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4859,21 +4873,21 @@
         <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>231</v>
+        <v>186</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4881,13 +4895,13 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
@@ -4896,19 +4910,19 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>129</v>
+        <v>228</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4921,7 +4935,7 @@
         <v>20</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>20</v>
@@ -4933,13 +4947,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>20</v>
+        <v>234</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4957,7 +4971,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4975,21 +4989,21 @@
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5012,18 +5026,20 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
       </c>
@@ -5035,7 +5051,7 @@
         <v>20</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>20</v>
@@ -5071,7 +5087,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5089,21 +5105,21 @@
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5111,13 +5127,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>20</v>
@@ -5126,15 +5142,17 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>250</v>
+        <v>101</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5147,7 +5165,7 @@
         <v>20</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>20</v>
@@ -5183,7 +5201,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5201,21 +5219,21 @@
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5238,17 +5256,15 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5297,7 +5313,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5315,21 +5331,21 @@
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5337,31 +5353,31 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>163</v>
+        <v>262</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5387,13 +5403,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>268</v>
+        <v>20</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>269</v>
+        <v>20</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5411,10 +5427,10 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>87</v>
@@ -5426,24 +5442,24 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>272</v>
+        <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5451,31 +5467,31 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>275</v>
+        <v>163</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5501,13 +5517,13 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>20</v>
+        <v>273</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5525,13 +5541,13 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
@@ -5540,16 +5556,16 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>20</v>
+        <v>275</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>105</v>
+        <v>276</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>20</v>
+        <v>277</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>20</v>
+        <v>278</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5568,7 +5584,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5580,15 +5596,17 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>101</v>
+        <v>280</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>102</v>
+        <v>281</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5637,19 +5655,19 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>104</v>
+        <v>279</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -5666,21 +5684,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5692,17 +5710,15 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5751,19 +5767,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5780,14 +5796,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>282</v>
+        <v>107</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5800,26 +5816,24 @@
         <v>20</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>283</v>
+        <v>109</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>284</v>
+        <v>110</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O33" t="s" s="2">
-        <v>200</v>
-      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5867,7 +5881,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>285</v>
+        <v>115</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5885,7 +5899,7 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>186</v>
+        <v>105</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
@@ -5903,35 +5917,39 @@
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5955,13 +5973,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>268</v>
+        <v>20</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>269</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5979,25 +5997,25 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
@@ -6008,10 +6026,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6034,13 +6052,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>250</v>
+        <v>163</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6067,13 +6085,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>20</v>
+        <v>273</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -6091,7 +6109,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -6118,12 +6136,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6137,22 +6155,22 @@
         <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>292</v>
+        <v>255</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6179,13 +6197,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>295</v>
+        <v>20</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>296</v>
+        <v>20</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -6203,7 +6221,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>87</v>
@@ -6221,21 +6239,21 @@
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>297</v>
+        <v>105</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>298</v>
+        <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>299</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6243,28 +6261,28 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6291,13 +6309,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>20</v>
+        <v>301</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -6315,13 +6333,13 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
@@ -6333,21 +6351,21 @@
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>105</v>
+        <v>302</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>20</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6358,7 +6376,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6370,13 +6388,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>101</v>
+        <v>280</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>102</v>
+        <v>306</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>103</v>
+        <v>307</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6427,19 +6445,19 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>104</v>
+        <v>305</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -6456,21 +6474,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6482,17 +6500,15 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6541,19 +6557,19 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -6570,14 +6586,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>282</v>
+        <v>107</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6590,26 +6606,24 @@
         <v>20</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>283</v>
+        <v>109</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>284</v>
+        <v>110</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O40" t="s" s="2">
-        <v>200</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6657,7 +6671,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>285</v>
+        <v>115</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6675,7 +6689,7 @@
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>186</v>
+        <v>105</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>20</v>
@@ -6686,42 +6700,46 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
       </c>
@@ -6745,13 +6763,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>295</v>
+        <v>20</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>296</v>
+        <v>20</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6769,25 +6787,25 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>20</v>
@@ -6798,10 +6816,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6824,13 +6842,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>250</v>
+        <v>141</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6857,13 +6875,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>20</v>
+        <v>301</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6881,7 +6899,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>87</v>
@@ -6908,12 +6926,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6924,29 +6942,27 @@
         <v>87</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>313</v>
+        <v>255</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N43" t="s" s="2">
         <v>316</v>
       </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6971,13 +6987,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>317</v>
+        <v>20</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>318</v>
+        <v>20</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -6995,13 +7011,13 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
@@ -7010,24 +7026,24 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>319</v>
+        <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>320</v>
+        <v>105</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>298</v>
+        <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>321</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7035,13 +7051,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>20</v>
@@ -7050,15 +7066,17 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7083,13 +7101,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -7107,13 +7125,13 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
@@ -7122,24 +7140,24 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>105</v>
+        <v>325</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7159,16 +7177,16 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7219,7 +7237,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7234,57 +7252,55 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>20</v>
+        <v>324</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AM45" t="s" s="2">
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="AN45" t="s" s="2">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>335</v>
-      </c>
       <c r="B46" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7309,13 +7325,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>20</v>
+        <v>335</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>20</v>
+        <v>336</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7333,7 +7349,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7348,38 +7364,38 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>341</v>
+        <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>20</v>
+        <v>341</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>20</v>
@@ -7388,15 +7404,17 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7445,13 +7463,13 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
@@ -7460,28 +7478,28 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>353</v>
+        <v>20</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7497,16 +7515,16 @@
         <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7557,7 +7575,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7572,28 +7590,28 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AL48" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>359</v>
-      </c>
       <c r="B49" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>20</v>
+        <v>358</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7603,16 +7621,16 @@
         <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>275</v>
+        <v>359</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>360</v>
@@ -7669,7 +7687,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7693,15 +7711,15 @@
         <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
         <v>364</v>
       </c>
-    </row>
-    <row r="50" hidden="true">
-      <c r="A50" t="s" s="2">
-        <v>365</v>
-      </c>
       <c r="B50" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7712,25 +7730,25 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>101</v>
+        <v>280</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>102</v>
+        <v>365</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>103</v>
+        <v>366</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7781,50 +7799,50 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>104</v>
+        <v>364</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>20</v>
+        <v>367</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>105</v>
+        <v>368</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -7836,17 +7854,15 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7895,19 +7911,19 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
@@ -7924,14 +7940,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>282</v>
+        <v>107</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7944,26 +7960,24 @@
         <v>20</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>283</v>
+        <v>109</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>284</v>
+        <v>110</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O52" t="s" s="2">
-        <v>200</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
       </c>
@@ -8011,7 +8025,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>285</v>
+        <v>115</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8029,7 +8043,7 @@
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>186</v>
+        <v>105</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>20</v>
@@ -8038,16 +8052,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8057,27 +8071,29 @@
         <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I53" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>313</v>
+        <v>108</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>369</v>
+        <v>288</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>370</v>
+        <v>289</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
       </c>
@@ -8101,13 +8117,13 @@
         <v>20</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>370</v>
+        <v>20</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>372</v>
+        <v>20</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -8125,7 +8141,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>368</v>
+        <v>290</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8137,27 +8153,27 @@
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>374</v>
+        <v>186</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>375</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8168,7 +8184,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>88</v>
@@ -8177,18 +8193,20 @@
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>250</v>
+        <v>318</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8213,13 +8231,13 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>20</v>
+        <v>375</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>20</v>
+        <v>377</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -8237,13 +8255,13 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
@@ -8252,7 +8270,7 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>20</v>
+        <v>378</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>379</v>
@@ -8289,20 +8307,18 @@
         <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>385</v>
-      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8366,24 +8382,24 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AL55" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="B56" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8394,10 +8410,10 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>20</v>
@@ -8406,15 +8422,17 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8463,13 +8481,13 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
@@ -8478,24 +8496,24 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>357</v>
+        <v>391</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AM56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN56" t="s" s="2">
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
         <v>395</v>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="B57" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8506,29 +8524,27 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J57" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="K57" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M57" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>400</v>
-      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8577,13 +8593,13 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
@@ -8592,24 +8608,24 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>405</v>
-      </c>
       <c r="B58" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8623,7 +8639,7 @@
         <v>87</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>20</v>
@@ -8632,16 +8648,16 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8691,7 +8707,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8706,56 +8722,56 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AM58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>412</v>
-      </c>
       <c r="B59" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>413</v>
+        <v>20</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>313</v>
+        <v>411</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8781,13 +8797,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>417</v>
+        <v>20</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>418</v>
+        <v>20</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -8805,13 +8821,13 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
@@ -8820,28 +8836,28 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>421</v>
+        <v>20</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8860,16 +8876,16 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>424</v>
+        <v>318</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8895,13 +8911,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>20</v>
+        <v>422</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>20</v>
+        <v>423</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -8919,7 +8935,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8934,28 +8950,28 @@
         <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>20</v>
+        <v>418</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8965,7 +8981,7 @@
         <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>20</v>
@@ -8974,15 +8990,17 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>275</v>
+        <v>429</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9031,7 +9049,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9046,24 +9064,24 @@
         <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>20</v>
+        <v>424</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>20</v>
+        <v>426</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>20</v>
+        <v>427</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9074,7 +9092,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -9083,16 +9101,16 @@
         <v>20</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>101</v>
+        <v>280</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>102</v>
+        <v>432</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>103</v>
+        <v>433</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9143,25 +9161,25 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>104</v>
+        <v>431</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>105</v>
+        <v>434</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>20</v>
@@ -9172,21 +9190,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -9198,17 +9216,15 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9257,19 +9273,19 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
@@ -9286,14 +9302,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>282</v>
+        <v>107</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9306,26 +9322,24 @@
         <v>20</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>283</v>
+        <v>109</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>284</v>
+        <v>110</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O64" t="s" s="2">
-        <v>200</v>
-      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>20</v>
       </c>
@@ -9373,7 +9387,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>285</v>
+        <v>115</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9391,7 +9405,7 @@
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>186</v>
+        <v>105</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>20</v>
@@ -9402,44 +9416,46 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>434</v>
+        <v>287</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>435</v>
+        <v>108</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>436</v>
+        <v>288</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>437</v>
+        <v>289</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
       </c>
@@ -9487,47 +9503,47 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>433</v>
+        <v>290</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>438</v>
+        <v>20</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>439</v>
+        <v>186</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>421</v>
+        <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>440</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>20</v>
+        <v>439</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>87</v>
@@ -9539,18 +9555,20 @@
         <v>20</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>313</v>
+        <v>440</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M66" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N66" s="2"/>
+      <c r="N66" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -9575,13 +9593,13 @@
         <v>20</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>444</v>
+        <v>20</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>445</v>
+        <v>20</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>20</v>
@@ -9599,10 +9617,10 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>87</v>
@@ -9614,16 +9632,16 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>20</v>
+        <v>443</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>105</v>
+        <v>444</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>20</v>
+        <v>426</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>20</v>
+        <v>445</v>
       </c>
     </row>
     <row r="67" hidden="true">
@@ -9654,13 +9672,13 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9687,13 +9705,13 @@
         <v>20</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>20</v>
+        <v>449</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>20</v>
+        <v>450</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>20</v>
@@ -9729,7 +9747,7 @@
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>450</v>
+        <v>105</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>20</v>
@@ -9754,7 +9772,7 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
@@ -9774,9 +9792,7 @@
       <c r="M68" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="N68" t="s" s="2">
-        <v>455</v>
-      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -9831,7 +9847,7 @@
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>20</v>
@@ -9843,21 +9859,21 @@
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="AM68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>457</v>
-      </c>
       <c r="B69" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9868,10 +9884,10 @@
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>20</v>
@@ -9880,7 +9896,7 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>275</v>
+        <v>457</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>458</v>
@@ -9939,13 +9955,13 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
@@ -9966,7 +9982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>462</v>
       </c>
@@ -9985,7 +10001,7 @@
         <v>87</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>20</v>
@@ -9994,15 +10010,17 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>101</v>
+        <v>280</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>102</v>
+        <v>463</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10051,7 +10069,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>104</v>
+        <v>462</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10063,13 +10081,13 @@
         <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>105</v>
+        <v>466</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>20</v>
@@ -10080,21 +10098,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
@@ -10106,17 +10124,15 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10165,19 +10181,19 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>20</v>
@@ -10194,14 +10210,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>282</v>
+        <v>107</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10214,26 +10230,24 @@
         <v>20</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>283</v>
+        <v>109</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>284</v>
+        <v>110</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O72" t="s" s="2">
-        <v>200</v>
-      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>20</v>
       </c>
@@ -10281,7 +10295,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>285</v>
+        <v>115</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10299,7 +10313,7 @@
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>186</v>
+        <v>105</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>20</v>
@@ -10310,42 +10324,46 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>466</v>
+        <v>108</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>467</v>
+        <v>288</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
       </c>
@@ -10393,31 +10411,31 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>465</v>
+        <v>290</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>469</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74" hidden="true">
@@ -10523,13 +10541,13 @@
         <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>20</v>
       </c>
     </row>
     <row r="75" hidden="true">
@@ -10560,13 +10578,13 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>313</v>
+        <v>476</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10593,13 +10611,13 @@
         <v>20</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>478</v>
+        <v>20</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>479</v>
+        <v>20</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>20</v>
@@ -10635,21 +10653,21 @@
         <v>20</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>481</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10672,13 +10690,13 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10705,13 +10723,13 @@
         <v>20</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>20</v>
@@ -10729,7 +10747,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10747,21 +10765,21 @@
         <v>20</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>105</v>
+        <v>485</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10772,7 +10790,7 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>20</v>
@@ -10784,20 +10802,16 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M77" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>492</v>
-      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>20</v>
       </c>
@@ -10824,10 +10838,10 @@
         <v>153</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>20</v>
@@ -10845,13 +10859,13 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>20</v>
@@ -10863,21 +10877,21 @@
         <v>20</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>495</v>
+        <v>105</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10900,16 +10914,20 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>497</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
       </c>
@@ -10933,13 +10951,13 @@
         <v>20</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>20</v>
@@ -10957,7 +10975,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10975,21 +10993,21 @@
         <v>20</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11012,13 +11030,13 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11048,10 +11066,10 @@
         <v>167</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>20</v>
@@ -11069,7 +11087,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11087,21 +11105,21 @@
         <v>20</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11112,7 +11130,7 @@
         <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>20</v>
@@ -11124,13 +11142,13 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>471</v>
+        <v>318</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11157,13 +11175,13 @@
         <v>20</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>20</v>
+        <v>512</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>20</v>
+        <v>513</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>20</v>
@@ -11181,13 +11199,13 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>20</v>
@@ -11208,7 +11226,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
         <v>516</v>
       </c>
@@ -11227,7 +11245,7 @@
         <v>87</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>20</v>
@@ -11236,7 +11254,7 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>313</v>
+        <v>476</v>
       </c>
       <c r="L81" t="s" s="2">
         <v>517</v>
@@ -11269,11 +11287,13 @@
         <v>20</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="Y81" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z81" t="s" s="2">
-        <v>519</v>
+        <v>20</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>20</v>
@@ -11309,21 +11329,21 @@
         <v>20</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>521</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11334,7 +11354,7 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>88</v>
@@ -11346,17 +11366,15 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="M82" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>525</v>
-      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -11381,13 +11399,11 @@
         <v>20</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>20</v>
+        <v>524</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>20</v>
@@ -11405,13 +11421,13 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>20</v>
@@ -11423,16 +11439,16 @@
         <v>20</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AM82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>20</v>
-      </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
         <v>527</v>
       </c>
@@ -11448,10 +11464,10 @@
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>20</v>
@@ -11460,15 +11476,17 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>101</v>
+        <v>280</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>102</v>
+        <v>528</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>529</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>530</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -11517,25 +11535,25 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>104</v>
+        <v>527</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>105</v>
+        <v>531</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>20</v>
@@ -11546,21 +11564,21 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>20</v>
@@ -11572,17 +11590,15 @@
         <v>20</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>20</v>
@@ -11631,19 +11647,19 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>20</v>
@@ -11660,14 +11676,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>282</v>
+        <v>107</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -11680,26 +11696,24 @@
         <v>20</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>283</v>
+        <v>109</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>284</v>
+        <v>110</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O85" t="s" s="2">
-        <v>200</v>
-      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>20</v>
       </c>
@@ -11747,7 +11761,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>285</v>
+        <v>115</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11765,7 +11779,7 @@
         <v>20</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>186</v>
+        <v>105</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>20</v>
@@ -11774,44 +11788,48 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I86" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I86" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="J86" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>471</v>
+        <v>108</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>531</v>
+        <v>288</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>20</v>
       </c>
@@ -11859,39 +11877,39 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>530</v>
+        <v>290</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>533</v>
+        <v>20</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>387</v>
+        <v>186</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>534</v>
+        <v>20</v>
       </c>
       <c r="AN86" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
         <v>535</v>
       </c>
-    </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>536</v>
-      </c>
       <c r="B87" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11899,13 +11917,13 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>20</v>
@@ -11914,17 +11932,15 @@
         <v>20</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>163</v>
+        <v>476</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M87" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>539</v>
-      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -11949,13 +11965,13 @@
         <v>20</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>540</v>
+        <v>20</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>541</v>
+        <v>20</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>20</v>
@@ -11973,10 +11989,10 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>87</v>
@@ -11988,24 +12004,24 @@
         <v>99</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>20</v>
+        <v>538</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>542</v>
+        <v>392</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>20</v>
+        <v>539</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>20</v>
+        <v>540</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12028,16 +12044,16 @@
         <v>20</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>313</v>
+        <v>163</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12063,13 +12079,13 @@
         <v>20</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>153</v>
+        <v>222</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>20</v>
@@ -12087,7 +12103,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12105,7 +12121,7 @@
         <v>20</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>20</v>
+        <v>547</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>20</v>
@@ -12116,10 +12132,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12142,15 +12158,17 @@
         <v>20</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>250</v>
+        <v>318</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>20</v>
@@ -12175,13 +12193,13 @@
         <v>20</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>20</v>
+        <v>552</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>20</v>
+        <v>553</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>20</v>
@@ -12199,7 +12217,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12217,7 +12235,7 @@
         <v>20</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>20</v>
@@ -12226,12 +12244,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12245,7 +12263,7 @@
         <v>87</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>20</v>
@@ -12254,13 +12272,13 @@
         <v>20</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>553</v>
+        <v>255</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12311,7 +12329,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12326,24 +12344,24 @@
         <v>99</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>386</v>
+        <v>20</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>556</v>
+        <v>384</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN90" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
         <v>557</v>
       </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>558</v>
-      </c>
       <c r="B91" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12357,7 +12375,7 @@
         <v>87</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>20</v>
@@ -12366,17 +12384,15 @@
         <v>20</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="M91" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="M91" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>562</v>
-      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>20</v>
@@ -12425,7 +12441,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12440,20 +12456,134 @@
         <v>99</v>
       </c>
       <c r="AK91" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="AL91" t="s" s="2">
+      <c r="B92" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K92" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AM91" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN91" t="s" s="2">
+      <c r="L92" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN91">
+  <autoFilter ref="A1:AN92">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12463,7 +12593,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI90">
+  <conditionalFormatting sqref="A2:AI91">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
